--- a/SeaBASS_variableNames.xlsx
+++ b/SeaBASS_variableNames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\GitHub_niskin\BWrepos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCB96C2-AE6B-44E5-B8CC-BB9AC93745C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BDB6C41-F8B0-4A15-9E4F-31D650013800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="2640" windowWidth="35160" windowHeight="16965" xr2:uid="{3F7459D6-1AF5-4BB4-A9E0-B154B06752D8}"/>
+    <workbookView xWindow="-24090" yWindow="3795" windowWidth="23265" windowHeight="16725" activeTab="1" xr2:uid="{3F7459D6-1AF5-4BB4-A9E0-B154B06752D8}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1925" uniqueCount="1406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="1411">
   <si>
     <t>Field name</t>
   </si>
@@ -4258,6 +4258,21 @@
   </si>
   <si>
     <t>Krista Longnecker 10 June 2026</t>
+  </si>
+  <si>
+    <t>KL changed one definition:</t>
+  </si>
+  <si>
+    <t>was:</t>
+  </si>
+  <si>
+    <t>A life science identifier from a recognized taxonomic reference database (e.g., World Register of Marine Species, AlgaeBase) at the lowest level that matches the data provider's category, for a manual identification matched to scientificNameID. Generally, the ROI corresponds to an occurrence assigned to a single taxonomic name.</t>
+  </si>
+  <si>
+    <t>is:</t>
+  </si>
+  <si>
+    <t>Krista Longnecker, updated 19 June 2026</t>
   </si>
 </sst>
 </file>
@@ -4301,9 +4316,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10071,7 +10089,7 @@
         <v>20</v>
       </c>
       <c r="C514" t="s">
-        <v>1068</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -11759,22 +11777,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{606BEEF7-06C3-449F-8C22-458DEE9BAB8A}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="65.28515625" customWidth="1"/>
+    <col min="3" max="3" width="70.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1403</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1405</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1408</v>
       </c>
     </row>
   </sheetData>
